--- a/questionnaire_templates/033_gifted_student_assessment_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/033_gifted_student_assessment_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -694,7 +694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Caregiver Comments</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>student_educator_comments</t>
+          <t>student_educator_comments_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Student Educator Comments 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Caregiver Email</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Caregiver Phone</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_by_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Submitted by</t>
+          <t>Submitted By 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1118,8 +1118,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'2nd_grade'}</t>
+          <t>2nd_grade</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': '2nd Grade'}</t>
+          <t>2nd Grade</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'3rd_grade'}</t>
+          <t>3rd_grade</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': '3rd Grade'}</t>
+          <t>3rd Grade</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'4th_grade'}</t>
+          <t>4th_grade</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': '4th Grade'}</t>
+          <t>4th Grade</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'educator'}</t>
+          <t>educator</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'Educator'}</t>
+          <t>Educator</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'caregiver'}</t>
+          <t>caregiver</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'Caregiver'}</t>
+          <t>Caregiver</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'athlete'}</t>
+          <t>athlete</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'Athlete'}</t>
+          <t>Athlete</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_31,_'name':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 31, 'name': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_40,_'name':_'american_indian_or_alaska_native'}</t>
+          <t>american_indian_or_alaska_native</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 40, 'name': 'American Indian or Alaska Native'}</t>
+          <t>American Indian or Alaska Native</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_41,_'name':_'asian'}</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 41, 'name': 'Asian'}</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_42,_'name':_'black_or_african_american'}</t>
+          <t>black_or_african_american</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 42, 'name': 'Black or African American'}</t>
+          <t>Black or African American</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_43,_'name':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 43, 'name': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_44,_'name':_'pacific_islander_or_hawaiian'}</t>
+          <t>pacific_islander_or_hawaiian</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 44, 'name': 'Pacific Islander or Hawaiian'}</t>
+          <t>Pacific Islander or Hawaiian</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_45,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 45, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_50,_'name':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 50, 'name': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_51,_'name':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 51, 'name': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_52,_'name':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 52, 'name': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_53,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 53, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_60,_'name':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 60, 'name': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_61,_'name':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 61, 'name': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_62,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 62, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_70,_'name':_'dyslexia'}</t>
+          <t>dyslexia</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 70, 'name': 'Dyslexia'}</t>
+          <t>Dyslexia</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_71,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 71, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_80,_'name':_"bachelor's_degree"}</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 80, 'name': "Bachelor's degree"}</t>
+          <t>Bachelor's degree</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_81,_'name':_"master's_degree"}</t>
+          <t>master's_degree</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 81, 'name': "Master's degree"}</t>
+          <t>Master's degree</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_82,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 82, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_90,_'name':_'0-2_years'}</t>
+          <t>0-2_years</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 90, 'name': '0-2 years'}</t>
+          <t>0-2 years</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_91,_'name':_'3-5_years'}</t>
+          <t>3-5_years</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 91, 'name': '3-5 years'}</t>
+          <t>3-5 years</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_92,_'name':_'6-10_years'}</t>
+          <t>6-10_years</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 92, 'name': '6-10 years'}</t>
+          <t>6-10 years</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_100,_'name':_'math'}</t>
+          <t>math</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 100, 'name': 'Math'}</t>
+          <t>Math</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_101,_'name':_'reading'}</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 101, 'name': 'Reading'}</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
@@ -1691,63 +1691,63 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_102,_'name':_'writing'}</t>
+          <t>writing</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 102, 'name': 'Writing'}</t>
+          <t>Writing</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_130,_'name':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 130, 'name': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_131,_'name':_'educator'}</t>
+          <t>educator</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 131, 'name': 'Educator'}</t>
+          <t>Educator</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_132,_'name':_'caregiver'}</t>
+          <t>caregiver</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 132, 'name': 'Caregiver'}</t>
+          <t>Caregiver</t>
         </is>
       </c>
     </row>
